--- a/sources/cp2.xlsx
+++ b/sources/cp2.xlsx
@@ -1185,12 +1185,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KCGM</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kalgoorlie Consolidated Gold Mines</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NSR</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northern Star Resources Ltd</t>
+          <t>Owner</t>
         </is>
       </c>
     </row>
